--- a/data/trans_orig/IP16_n_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R-Clase-trans_orig.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>449</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13696</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -2408,12 +2408,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17603</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2493,12 +2493,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12298</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3080,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>35857</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28010</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>38198</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52508</t>
+          <t>52299</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>32967</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13762</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4985,12 +4985,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15249</t>
+          <t>15233</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>29196</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>45386</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>40941</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>58851</t>
+          <t>58759</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>76321</t>
+          <t>75084</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>100274</t>
+          <t>98600</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5207,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>58006</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>73907</t>
+          <t>74622</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>72527</t>
+          <t>72340</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>91336</t>
+          <t>91088</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>134820</t>
+          <t>135280</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>159406</t>
+          <t>159721</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16330</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>34651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41548</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -6674,12 +6674,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -6785,12 +6785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21406</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26149</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33071</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -7346,12 +7346,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>504</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -7457,12 +7457,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11803</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -8018,12 +8018,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>34768</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43860</t>
+          <t>43465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46469</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55792</t>
+          <t>55748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>85296</t>
+          <t>85502</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>97618</t>
+          <t>97549</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -8690,12 +8690,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8705,12 +8705,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26310</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18376</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>25272</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>39842</t>
+          <t>39794</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9923,12 +9923,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>28718</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>26483</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10084,12 +10084,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>50422</t>
+          <t>50295</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -10145,12 +10145,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>107308</t>
+          <t>107051</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>122123</t>
+          <t>122295</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>118766</t>
+          <t>116953</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>132974</t>
+          <t>132950</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10195,12 +10195,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>230747</t>
+          <t>230699</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>250365</t>
+          <t>251089</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10230,12 +10230,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10955,12 +10955,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11025,12 +11025,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -11051,12 +11051,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11121,12 +11121,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>32410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11647,12 +11647,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11682,12 +11682,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>29787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -12284,12 +12284,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12299,12 +12299,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -12395,12 +12395,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12465,12 +12465,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12480,12 +12480,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -12956,12 +12956,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -13067,12 +13067,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37082</t>
+          <t>37089</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43962</t>
+          <t>44028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13082,12 +13082,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>27529</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33313</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13117,12 +13117,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13137,12 +13137,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>67408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76128</t>
+          <t>76569</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13698,12 +13698,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13713,12 +13713,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -13739,12 +13739,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>25855</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13754,12 +13754,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13774,12 +13774,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22880</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13789,12 +13789,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13809,12 +13809,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>39195</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47656</t>
+          <t>47780</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13824,12 +13824,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14335,12 +14335,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14350,12 +14350,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14370,12 +14370,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14385,12 +14385,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -14426,7 +14426,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14461,12 +14461,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14496,12 +14496,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -14972,12 +14972,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>20848</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14987,12 +14987,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>20755</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15022,12 +15022,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>21227</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>36864</t>
+          <t>37681</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -15083,12 +15083,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>101313</t>
+          <t>101824</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>112351</t>
+          <t>113303</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15098,12 +15098,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>95520</t>
+          <t>95644</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>107052</t>
+          <t>107381</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>201246</t>
+          <t>201395</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>217472</t>
+          <t>217520</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -15696,7 +15696,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -15817,12 +15817,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -15852,12 +15852,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -15878,12 +15878,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -15893,12 +15893,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -15913,12 +15913,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -15928,12 +15928,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -15948,12 +15948,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21388</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -15963,12 +15963,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -15989,12 +15989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -16004,12 +16004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -16024,12 +16024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -16039,12 +16039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -16059,12 +16059,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42154</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16444,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -16509,12 +16509,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -16550,12 +16550,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16565,12 +16565,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16585,12 +16585,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16600,12 +16600,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16635,12 +16635,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -16661,12 +16661,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -16696,12 +16696,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16711,12 +16711,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16731,12 +16731,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36265</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16746,12 +16746,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -17222,12 +17222,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>388</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -17237,12 +17237,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -17257,12 +17257,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -17272,12 +17272,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -17292,12 +17292,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17307,12 +17307,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -17333,12 +17333,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -17348,12 +17348,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -17368,12 +17368,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -17383,12 +17383,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -17403,12 +17403,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>21927</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17418,12 +17418,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -17677,7 +17677,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -17783,12 +17783,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -17798,12 +17798,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17818,12 +17818,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>12577</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -17894,12 +17894,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -17909,12 +17909,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>23278</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -17944,12 +17944,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17964,12 +17964,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38779</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -17979,12 +17979,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -18005,12 +18005,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49376</t>
+          <t>50196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70866</t>
+          <t>71288</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -18020,12 +18020,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18040,12 +18040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28640</t>
+          <t>29024</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18055,12 +18055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18075,12 +18075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>82711</t>
+          <t>84871</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112447</t>
+          <t>114647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18090,12 +18090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>389</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -18470,12 +18470,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -18495,7 +18495,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -18525,12 +18525,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -18540,12 +18540,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -18566,12 +18566,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18581,12 +18581,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18601,12 +18601,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -18616,12 +18616,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -18636,12 +18636,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18651,12 +18651,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -18677,12 +18677,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>21292</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18692,12 +18692,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18712,12 +18712,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18727,12 +18727,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -18747,12 +18747,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>49133</t>
+          <t>48642</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -18762,12 +18762,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -19071,7 +19071,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -19132,7 +19132,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19147,7 +19147,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19217,7 +19217,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -19238,12 +19238,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19253,12 +19253,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19273,12 +19273,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19288,12 +19288,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19308,12 +19308,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19323,12 +19323,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -19349,12 +19349,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -19364,12 +19364,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19384,12 +19384,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19399,12 +19399,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19419,12 +19419,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11787</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>20412</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19434,12 +19434,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,38%</t>
         </is>
       </c>
     </row>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19597,7 +19597,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19667,7 +19667,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -19688,12 +19688,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19703,12 +19703,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19758,12 +19758,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -19799,12 +19799,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -19814,12 +19814,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -19834,12 +19834,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19849,12 +19849,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19869,12 +19869,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19884,12 +19884,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -19910,12 +19910,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>51775</t>
+          <t>52310</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -19925,12 +19925,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -19945,12 +19945,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>40737</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>61239</t>
+          <t>61597</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -19960,12 +19960,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>69200</t>
+          <t>68078</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>106782</t>
+          <t>106114</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -19995,12 +19995,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -20021,12 +20021,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>109471</t>
+          <t>110170</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>143981</t>
+          <t>145514</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -20036,12 +20036,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -20056,12 +20056,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>107142</t>
+          <t>105534</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>128629</t>
+          <t>128803</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20071,12 +20071,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>223685</t>
+          <t>224450</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>268807</t>
+          <t>270350</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20106,12 +20106,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
